--- a/docs/ValueSet-ahip-relationship-status.xlsx
+++ b/docs/ValueSet-ahip-relationship-status.xlsx
@@ -50,7 +50,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T00:00:00-04:00</t>
+    <t>2026-08-25T00:00:00-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -86,7 +86,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Based on HL7 Marital Status Value Set</t>
+    <t>Used as the answer options for the relationship status question in the SOGI and Relationship Status Section.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -152,22 +152,22 @@
     <t>DATI</t>
   </si>
   <si>
-    <t>Dating (non-committed relationship)</t>
+    <t>Dating (in a non-committed relationship with one person or more than one person)</t>
   </si>
   <si>
     <t>MONR</t>
   </si>
   <si>
-    <t>Monogamous Relationship (In a committed relationship with one person but not married</t>
+    <t>In a committed relationship with one person but not married (monogamous relationship)</t>
   </si>
   <si>
     <t>POLY</t>
   </si>
   <si>
-    <t>Polyamorous Relationship (In a committed relationship with more than one person)</t>
-  </si>
-  <si>
-    <t>http://ahip.org/demographics/ImplementationGuide/ahip.demo/CodeSystem/ahip-demo-additional-relationship-status-codes</t>
+    <t>In a committed relationship with more than one person (polyamorous relationship)</t>
+  </si>
+  <si>
+    <t>http://ahip.org/demographics/CodeSystem/ahip-demo-additional-relationship-status-codes</t>
   </si>
   <si>
     <t>PSIN</t>
@@ -182,7 +182,7 @@
     <t>I choose not to respond at this time</t>
   </si>
   <si>
-    <t>http://ahip.org/demographics/ImplementationGuide/ahip.demo/CodeSystem/AHIPDemoAdditionalNullFlavor</t>
+    <t>http://ahip.org/demographics/CodeSystem/AHIP-Demo-Additional-NullFlavor</t>
   </si>
 </sst>
 </file>

--- a/docs/ValueSet-ahip-relationship-status.xlsx
+++ b/docs/ValueSet-ahip-relationship-status.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="54">
   <si>
     <t>Property</t>
   </si>
@@ -168,12 +168,6 @@
   </si>
   <si>
     <t>http://ahip.org/demographics/CodeSystem/ahip-demo-additional-relationship-status-codes</t>
-  </si>
-  <si>
-    <t>PSIN</t>
-  </si>
-  <si>
-    <t>Please specify if not listed above</t>
   </si>
   <si>
     <t>CNTR</t>
@@ -596,7 +590,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -621,26 +615,18 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>54</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-ahip-relationship-status.xlsx
+++ b/docs/ValueSet-ahip-relationship-status.xlsx
@@ -10,12 +10,13 @@
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
     <sheet name="Include #2" r:id="rId6" sheetId="4"/>
+    <sheet name="Include #3" r:id="rId7" sheetId="5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="57">
   <si>
     <t>Property</t>
   </si>
@@ -95,7 +96,8 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Used by permission of HL7 International, all rights reserved Creative Commons License</t>
+    <t>This material derives from the HL7 Terminology (THO). THO is copyright ©1989+ Health Level Seven International and is made available under the CC0 designation. For more licensing information see: https://terminology.hl7.org/license.html
+This value set includes content developed through the DEMo Initiative and is subject to joint copyright of America's Health Insurance Plans (AHIP) and Health Level Seven International (HL7).</t>
   </si>
   <si>
     <t>Immutable</t>
@@ -152,22 +154,31 @@
     <t>DATI</t>
   </si>
   <si>
-    <t>Dating (in a non-committed relationship with one person or more than one person)</t>
+    <t>Dating (Non-committed relationship)</t>
   </si>
   <si>
     <t>MONR</t>
   </si>
   <si>
-    <t>In a committed relationship with one person but not married (monogamous relationship)</t>
+    <t>Monogamous relationship (Committed relationship with one person)</t>
   </si>
   <si>
     <t>POLY</t>
   </si>
   <si>
-    <t>In a committed relationship with more than one person (polyamorous relationship)</t>
-  </si>
-  <si>
-    <t>http://ahip.org/demographics/CodeSystem/ahip-demo-additional-relationship-status-codes</t>
+    <t>Polyamorous relationship (Committed relationship with more than one person)</t>
+  </si>
+  <si>
+    <t>http://ahip.org/demographics/CodeSystem/ahip-demo-temporary-codes</t>
+  </si>
+  <si>
+    <t>ASKU</t>
+  </si>
+  <si>
+    <t>I don't know</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/CodeSystem/v3-NullFlavor</t>
   </si>
   <si>
     <t>CNTR</t>
@@ -176,7 +187,7 @@
     <t>I choose not to respond at this time</t>
   </si>
   <si>
-    <t>http://ahip.org/demographics/CodeSystem/AHIP-Demo-Additional-NullFlavor</t>
+    <t>http://ahip.org/demographics/CodeSystem/ahip-demo-additional-nullFlavor</t>
   </si>
 </sst>
 </file>
@@ -632,4 +643,50 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>